--- a/test_single_college.xlsx
+++ b/test_single_college.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Colleges" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Faculty" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O2"/>
+  <dimension ref="A1:O3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -527,14 +528,405 @@
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>WEB(7p)</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>https://indore.nic.in/en/public-utility/indian-institute-of-technology-indore/</t>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Maulana Azad National Institute of Technology</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Madhya pradesh</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Link Road Number 3, Near Kali Mata Mandir   India</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Engineering</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>4556</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>officeofdirector@manit.ac.in</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>0755-4051000</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Karunesh Kumar Shukla</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Karunesh Kumar Shukla</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>Director</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>NIRF(100.0) + CollegeDunia(83) + CD-staff</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>http://www.manit.ac.in/</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>College Name</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>State</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Faculty Name</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Designation</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Department</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Qualification</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Maulana Azad National Institute of Technology</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Madhya pradesh</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Ashutosh Sharma</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Professor</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Departnment of Architecture Planning</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>ashutosh9826055792@gmail.com</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>9826055792</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Post Doc, Ph.D, MURP, BArch</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Maulana Azad National Institute of Technology</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Madhya pradesh</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Alka Bharat</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Professor</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Departnment of Architecture Planning</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>alka_bharat@yahoo.com</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>9826296046</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>B.Arch, MURP, Ph.D</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Maulana Azad National Institute of Technology</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Madhya pradesh</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Manmohan Kapshe</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Professor</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Departnment of Architecture Planning</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>kapshem@manit.ac.in</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>755 4051100</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Ph.D</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Maulana Azad National Institute of Technology</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Madhya pradesh</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Nitin Dindorker</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Professor</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Departnment of Civil Engineering</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>dindorkar_nit@rediffmail.com</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0755 4051204</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Ph.D</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Maulana Azad National Institute of Technology</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Madhya pradesh</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Vijaya Kumar Bulasara</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Associate Professor &amp; HOD</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Departnment of Chemical Engineering</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>84371-668O6</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Ph.D.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Maulana Azad National Institute of Technology</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Madhya pradesh</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Meenu Chawla</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Professor</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Departnment of Computer Science and Engineering</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>07554051302</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Ph.D CSE</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Maulana Azad National Institute of Technology</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Madhya pradesh</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Rajesh Kumar Nema</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Professor</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Departnment of Electrical Engineering</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Ph.D (Photovoltaic Inverter.), M.Tech (Heavy Electrical Equipments), B.E.( Electrical Engineering)</t>
         </is>
       </c>
     </row>
